--- a/Data Files/Auto/ReentradaPropostaAuto/ReentradaPropostaAuto.xlsx
+++ b/Data Files/Auto/ReentradaPropostaAuto/ReentradaPropostaAuto.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="30">
   <si>
     <t xml:space="preserve">Mensagem </t>
   </si>
@@ -83,6 +83,42 @@
   </si>
   <si>
     <t>Alerta: Falha ao importar os dados.  Erro de cálculo - (RL)</t>
+  </si>
+  <si>
+    <t>Emissão realizada: 134038761 / 0 / 0</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao importar os dados.  LOCALIDADE INEXISTENTE</t>
+  </si>
+  <si>
+    <t>Emissão realizada: 134056034 / 0 / 0</t>
+  </si>
+  <si>
+    <t>Emissão realizada: 134062405 / 0 / 0</t>
+  </si>
+  <si>
+    <t>Emissão realizada: 134086971 / 0 / 0</t>
+  </si>
+  <si>
+    <t>Emissão realizada: 134184114 / 0 / 0</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao importar os dados.  Campo Placa da tela dados de risco é obrigatório para emissão</t>
+  </si>
+  <si>
+    <t>Emissão realizada: 134185487 / 0 / 0</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao importar os dados.  E-mail não permitido, já utilizado no cadastro do corretor.</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao importar os dados.  Fonte da apólice anterior informada inválida</t>
+  </si>
+  <si>
+    <t>Emissão realizada: 134253753 / 0 / 0</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao importar os dados.  Saldo no Conta Corrente insuficiente para efetivação desta proposta. Favor ajustar as condições comerciais inseridas na cotação e tente novamente</t>
   </si>
 </sst>
 </file>
@@ -547,7 +583,7 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
